--- a/artfynd/A 43704-2021 artfynd.xlsx
+++ b/artfynd/A 43704-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43704-2021 artfynd.xlsx
+++ b/artfynd/A 43704-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117291266</v>
+        <v>117291385</v>
       </c>
       <c r="B7" t="n">
-        <v>100709</v>
+        <v>57789</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,48 +1278,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1449</v>
+        <v>102995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hällebräcka</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saxifraga osloënsis</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Knaben</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Solgläntan, hällebräcka 350 m V om, , Srm</t>
+          <t>Solgläntan 300 m V, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563745</v>
+        <v>563870</v>
       </c>
       <c r="R7" t="n">
-        <v>6545444</v>
+        <v>6545439</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1344,11 +1346,6 @@
           <t>Västra Vingåker</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>D-Vin-0053</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>2024-05-26</t>
@@ -1359,18 +1356,12 @@
           <t>2024-05-26</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Vedupplag på platsen. En del av lokalen, längs en mindre skogsbilväg spolierad pga skogsmaskiner.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1385,125 +1376,7 @@
           <t>Håkan Lernefalk</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>117291385</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57789</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>102995</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Buskskvätta</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Saxicola rubetra</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Solgläntan 300 m V, Srm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>563870</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6545439</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Vingåker</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Västra Vingåker</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Håkan Lernefalk</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Håkan Lernefalk</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43704-2021 artfynd.xlsx
+++ b/artfynd/A 43704-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>428810</v>
+        <v>415636</v>
       </c>
       <c r="B2" t="n">
-        <v>99120</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,29 +703,20 @@
           <t>Knaben</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Solgläntan 350 m VSV-ut, Srm</t>
+          <t>Solgläntan, hällebräcka 350 m V om, , Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563758.9988137914</v>
+        <v>563745</v>
       </c>
       <c r="R2" t="n">
-        <v>6545445.139729654</v>
+        <v>6545444</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,29 +738,24 @@
           <t>Västra Vingåker</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>D-Vin-0053</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2006-06-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2006-06-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1987-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Östra hällen, f.d. timmerupplag. Igenväxande</t>
+          <t>Observatör: Folke Lind</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,39 +767,35 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>översilad basisk häll</t>
-        </is>
-      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>D-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>D-län Floraväktarna</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Kärlväxtinventering D-län</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>418858</v>
+        <v>428593</v>
       </c>
       <c r="B3" t="n">
-        <v>99120</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,27 +822,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Solgläntan, hällebräcka 350 m V om, , Srm</t>
+          <t>Solgläntan 350 m VSV-ut, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563745.1000285748</v>
+        <v>563730</v>
       </c>
       <c r="R3" t="n">
-        <v>6545443.879307134</v>
+        <v>6545447</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,34 +864,19 @@
           <t>Västra Vingåker</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>D-Vin-0053</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1998-05-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1998-05-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på 5x30 m Timmerupplagsplats med sönderkört jordtäcke och delvis berghällar</t>
+          <t>Västra hällen. Stor grushög tippad på lokalen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,75 +890,79 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barr-/lövblandskog, Timmerupplagsplats med sönderk Barr-/lövblandskog</t>
+          <t>översilad basisk häll</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>D-län Floraväktarna</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>D-län Floraväktarna, Bo Karlsson, Lennart Karlén</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Kärlväxtinventering D-län</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111669464</v>
+        <v>428810</v>
       </c>
       <c r="B4" t="n">
-        <v>57067</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>1449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Hällebräcka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Saxifraga osloënsis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Solgläntan, 350 m väster, Srm</t>
+          <t>Solgläntan 350 m VSV-ut, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563744</v>
+        <v>563759</v>
       </c>
       <c r="R4" t="n">
         <v>6545445</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1020,12 +986,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2006-06-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2006-06-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Östra hällen, f.d. timmerupplag. Igenväxande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,69 +1007,82 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>översilad basisk häll</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering D-län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111669462</v>
+        <v>444702</v>
       </c>
       <c r="B5" t="n">
-        <v>56890</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102995</v>
+        <v>1449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Hällebräcka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Saxifraga osloënsis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Solgläntan, 350 m väster, Srm</t>
+          <t>Solgläntan 350 m v, Äng 400 m ö, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563744</v>
+        <v>563746</v>
       </c>
       <c r="R5" t="n">
-        <v>6545445</v>
+        <v>6545457</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,12 +1106,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2009-05-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2009-05-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>liten berghäll intill väg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,16 +1127,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Berghäll</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Berghäll</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>D-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>D-län Floraväktarna</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1157,12 +1156,7 @@
         <v>111669452</v>
       </c>
       <c r="B6" t="n">
-        <v>99136</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,19 +1260,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117291385</v>
+        <v>111669462</v>
       </c>
       <c r="B7" t="n">
-        <v>57789</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1299,32 +1288,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Solgläntan 300 m V, Srm</t>
+          <t>Solgläntan, 350 m väster, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563870</v>
+        <v>563744</v>
       </c>
       <c r="R7" t="n">
-        <v>6545439</v>
+        <v>6545445</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1348,12 +1325,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,15 +1345,323 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>117291385</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58463</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Solgläntan 300 m V, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>563870</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6545439</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Håkan Lernefalk</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Håkan Lernefalk</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>111669464</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Solgläntan, 350 m väster, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>563744</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6545445</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>85822871</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Solgläntan 300 m V, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>563870</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6545439</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-05-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-05-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Lernefalk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Lernefalk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43704-2021 artfynd.xlsx
+++ b/artfynd/A 43704-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/415636</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
           <t>Kärlväxtinventering D-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/428593</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
           <t>Kärlväxtinventering D-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/428810</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,6 +1170,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/444702</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111669452</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1354,6 +1384,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111669462</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117291385</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111669464</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,8 +1707,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85822871</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>